--- a/deliverables/Task 2/Y2A_model_iteration_log.xlsx
+++ b/deliverables/Task 2/Y2A_model_iteration_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edubuas-my.sharepoint.com/personal/buckens_m_buas_nl/Documents/2C/Y2C-2425/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rzvn1\Documents\git-school\fae2-nlpr-group-group-12-1\deliverables\Task 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{A91E47EE-1B7B-4C21-94BB-219C34D1CD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE4174E9-6336-48BE-8495-A13DF4591228}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1FF47F-2611-470F-8C4E-7ADBEA2FD44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D8ECC7B-96E6-4221-81CD-57BD062A831A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model Iteration Log" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <si>
     <t>Model iteration log</t>
   </si>
@@ -138,6 +138,69 @@
   <si>
     <t>Features used 
 (if applicable)</t>
+  </si>
+  <si>
+    <t>Logistic Regression</t>
+  </si>
+  <si>
+    <t>scikit-learn</t>
+  </si>
+  <si>
+    <t>final_dataset.csv</t>
+  </si>
+  <si>
+    <t>features.py (baseline)</t>
+  </si>
+  <si>
+    <t>80/0/20</t>
+  </si>
+  <si>
+    <t>Sentiment/word2vec embeddings/bert embeddings</t>
+  </si>
+  <si>
+    <t>Sentiment reshaped</t>
+  </si>
+  <si>
+    <t>max_iter = 1000</t>
+  </si>
+  <si>
+    <t>Quick and simple model, can be used as baseline</t>
+  </si>
+  <si>
+    <t>Very low scores,does not catch all emotions</t>
+  </si>
+  <si>
+    <t>This model is going to be used as a baseline for other models</t>
+  </si>
+  <si>
+    <t>Filip, Razvan</t>
+  </si>
+  <si>
+    <t>Gaussian Naïve Bayes</t>
+  </si>
+  <si>
+    <t>var_smoothing=0.0005</t>
+  </si>
+  <si>
+    <t>Works good with less data</t>
+  </si>
+  <si>
+    <t>The worst scores overall</t>
+  </si>
+  <si>
+    <t>Linear SVC</t>
+  </si>
+  <si>
+    <t>penalty='l2', loss='squared_hinge', C=500.0, multi_class='ovr', fit_intercept=True,</t>
+  </si>
+  <si>
+    <t>Good for separating  linear data</t>
+  </si>
+  <si>
+    <t>Horrible at separating non-linear data</t>
+  </si>
+  <si>
+    <t>Worst performing of them all</t>
   </si>
 </sst>
 </file>
@@ -376,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -474,6 +537,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -810,31 +876,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A5CD43-FACF-4F92-BDE3-5E7B47D72998}">
   <dimension ref="B2:U51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="6.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="36" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="33.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="30.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.28515625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="20.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="33.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -856,7 +922,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="2:21" ht="24" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:21" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
@@ -880,7 +946,7 @@
       <c r="T3" s="29"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -901,7 +967,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6"/>
       <c r="C5" s="18" t="s">
         <v>2</v>
@@ -924,7 +990,7 @@
       <c r="S5" s="18"/>
       <c r="T5" s="19"/>
     </row>
-    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
       <c r="C6" s="18" t="s">
         <v>3</v>
@@ -947,7 +1013,7 @@
       <c r="S6" s="18"/>
       <c r="T6" s="19"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
       <c r="C7" s="18"/>
       <c r="D7" s="20"/>
@@ -968,7 +1034,7 @@
       <c r="S7" s="18"/>
       <c r="T7" s="19"/>
     </row>
-    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -989,7 +1055,7 @@
       <c r="S8" s="18"/>
       <c r="T8" s="19"/>
     </row>
-    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16"/>
       <c r="C9" s="30" t="s">
         <v>1</v>
@@ -1024,7 +1090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
@@ -1079,76 +1145,170 @@
       <c r="S10" s="25"/>
       <c r="T10" s="26"/>
     </row>
-    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
         <v>1</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="C11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="34">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="L11" s="34">
+        <v>0.43</v>
+      </c>
+      <c r="M11" s="34">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="N11" s="34">
+        <v>0.38700000000000001</v>
+      </c>
       <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
+      <c r="P11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="T11" s="11"/>
     </row>
-    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>2</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="C12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.33300000000000002</v>
+      </c>
       <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="P12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
+      <c r="S12" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="T12" s="11"/>
     </row>
-    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="9">
         <v>3</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="C13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="L13" s="10">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.03</v>
+      </c>
       <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
+      <c r="P13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="T13" s="11"/>
     </row>
-    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="9">
         <v>4</v>
       </c>
@@ -1171,7 +1331,7 @@
       <c r="S14" s="10"/>
       <c r="T14" s="11"/>
     </row>
-    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -1194,7 +1354,7 @@
       <c r="S15" s="10"/>
       <c r="T15" s="11"/>
     </row>
-    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="9">
         <v>6</v>
       </c>
@@ -1217,7 +1377,7 @@
       <c r="S16" s="10"/>
       <c r="T16" s="11"/>
     </row>
-    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="9">
         <v>7</v>
       </c>
@@ -1240,7 +1400,7 @@
       <c r="S17" s="10"/>
       <c r="T17" s="11"/>
     </row>
-    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9">
         <v>8</v>
       </c>
@@ -1263,7 +1423,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="11"/>
     </row>
-    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="9">
         <v>9</v>
       </c>
@@ -1286,7 +1446,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="11"/>
     </row>
-    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -1309,7 +1469,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="11"/>
     </row>
-    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9">
         <v>11</v>
       </c>
@@ -1332,7 +1492,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="11"/>
     </row>
-    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9">
         <v>12</v>
       </c>
@@ -1355,7 +1515,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="11"/>
     </row>
-    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9">
         <v>13</v>
       </c>
@@ -1378,7 +1538,7 @@
       <c r="S23" s="10"/>
       <c r="T23" s="11"/>
     </row>
-    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9">
         <v>14</v>
       </c>
@@ -1401,7 +1561,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="11"/>
     </row>
-    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9">
         <v>15</v>
       </c>
@@ -1424,7 +1584,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="11"/>
     </row>
-    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9">
         <v>16</v>
       </c>
@@ -1447,7 +1607,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="11"/>
     </row>
-    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9">
         <v>17</v>
       </c>
@@ -1470,7 +1630,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="11"/>
     </row>
-    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="9">
         <v>18</v>
       </c>
@@ -1493,7 +1653,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="11"/>
     </row>
-    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="9">
         <v>19</v>
       </c>
@@ -1516,7 +1676,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="11"/>
     </row>
-    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9">
         <v>20</v>
       </c>
@@ -1539,7 +1699,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="11"/>
     </row>
-    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="9">
         <v>21</v>
       </c>
@@ -1562,7 +1722,7 @@
       <c r="S31" s="10"/>
       <c r="T31" s="11"/>
     </row>
-    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="9">
         <v>22</v>
       </c>
@@ -1585,7 +1745,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="11"/>
     </row>
-    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="9">
         <v>23</v>
       </c>
@@ -1608,7 +1768,7 @@
       <c r="S33" s="10"/>
       <c r="T33" s="11"/>
     </row>
-    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="9">
         <v>24</v>
       </c>
@@ -1631,7 +1791,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="11"/>
     </row>
-    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="9">
         <v>25</v>
       </c>
@@ -1654,7 +1814,7 @@
       <c r="S35" s="10"/>
       <c r="T35" s="11"/>
     </row>
-    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="9">
         <v>26</v>
       </c>
@@ -1677,7 +1837,7 @@
       <c r="S36" s="10"/>
       <c r="T36" s="11"/>
     </row>
-    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="9">
         <v>27</v>
       </c>
@@ -1700,7 +1860,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="11"/>
     </row>
-    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="9">
         <v>28</v>
       </c>
@@ -1723,7 +1883,7 @@
       <c r="S38" s="10"/>
       <c r="T38" s="11"/>
     </row>
-    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="9">
         <v>29</v>
       </c>
@@ -1746,7 +1906,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="11"/>
     </row>
-    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="9">
         <v>30</v>
       </c>
@@ -1769,7 +1929,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="11"/>
     </row>
-    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="9">
         <v>31</v>
       </c>
@@ -1792,7 +1952,7 @@
       <c r="S41" s="10"/>
       <c r="T41" s="11"/>
     </row>
-    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="9">
         <v>32</v>
       </c>
@@ -1815,7 +1975,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="9">
         <v>33</v>
       </c>
@@ -1838,7 +1998,7 @@
       <c r="S43" s="10"/>
       <c r="T43" s="11"/>
     </row>
-    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="9">
         <v>34</v>
       </c>
@@ -1861,7 +2021,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="11"/>
     </row>
-    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="9">
         <v>35</v>
       </c>
@@ -1884,7 +2044,7 @@
       <c r="S45" s="10"/>
       <c r="T45" s="11"/>
     </row>
-    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="9">
         <v>36</v>
       </c>
@@ -1907,7 +2067,7 @@
       <c r="S46" s="10"/>
       <c r="T46" s="11"/>
     </row>
-    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="9">
         <v>37</v>
       </c>
@@ -1930,7 +2090,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="11"/>
     </row>
-    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="9">
         <v>38</v>
       </c>
@@ -1953,7 +2113,7 @@
       <c r="S48" s="10"/>
       <c r="T48" s="11"/>
     </row>
-    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="9">
         <v>39</v>
       </c>
@@ -1976,7 +2136,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="11"/>
     </row>
-    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="12">
         <v>40</v>
       </c>
@@ -1999,7 +2159,7 @@
       <c r="S50" s="13"/>
       <c r="T50" s="14"/>
     </row>
-    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:20" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="15" t="s">
         <v>8</v>
       </c>
